--- a/public/assets/PWP_14_Day_Plan_Upload_Template.xlsx
+++ b/public/assets/PWP_14_Day_Plan_Upload_Template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" r:id="R3d50f78cd0ea4cd3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R2606f0d9ab484fa2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" r:id="R14c4867d5c66437d"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="1" r:id="R47f7be86d368426f"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R431e07ff529f40a8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" r:id="R120d9e54455b4a3d"/>
   </sheets>
 </workbook>
 </file>
@@ -928,12 +928,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="37"/>
+      <c r="A6" s="33" t="str">
+        <v>L-13</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="34" t="str">
+        <v>RUN</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <v>Crushing / Support</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="33"/>
@@ -2488,7 +2500,6 @@
       <c r="F200" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F200"/>
   <dataValidations count="5">
     <dataValidation type="list" sqref="A2:A200">
       <formula1>Lists!$C$2:$C$13</formula1>
@@ -2778,6 +2789,22 @@
       <c r="D24" s="118" t="str"/>
       <c r="E24" s="118" t="str"/>
       <c r="F24" s="119" t="str"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Crusher special rule</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Crusher demand is covered from available surplus and never creates an Agency request.</v>
+      </c>
+      <c r="C26" t="str">
+        <v>L-13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -2970,6 +2997,17 @@
         <v>DWC</v>
       </c>
     </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>L-13</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Crusher</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Crusher</v>
+      </c>
+    </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="139" t="str">
         <v>These Machine IDs match the supplied V2 project. During import, the application always validates against its live current Machines list.</v>
